--- a/survey_templates/039_skincare_routine_finder_quiz--survey_templates.xlsx
+++ b/survey_templates/039_skincare_routine_finder_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,8 +750,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,12 +779,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Dry'}</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'oily'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Oily'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'sensitive'}</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Sensitive'}</t>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'aging'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Aging'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'hyper-pigmentation'}</t>
+          <t>hyper-pigmentation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Hyper-pigmentation'}</t>
+          <t>Hyper-pigmentation</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'irritation'}</t>
+          <t>irritation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Irritation'}</t>
+          <t>Irritation</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'redness'}</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Redness'}</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'morning_and_night'}</t>
+          <t>morning_and_night</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Morning and Night'}</t>
+          <t>Morning and Night</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'night'}</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Night'}</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
